--- a/Tecan/Evaluation Folder/Input/DOE 12.7.xlsx
+++ b/Tecan/Evaluation Folder/Input/DOE 12.7.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0f9b98384af4391/Desktop/Morph/Python/Single/Tecan/Tecan_Reader/Evaluation Folder/Input/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0f9b98384af4391/Desktop/Morph/Python/Foraging/Tecan/Tecan_Reader/Evaluation Folder/Input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="11_1A45D1421249410336650213469F00B47C5A11AB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{142274BB-BFC6-47EA-83B9-344CD8F91FF2}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="11_1A45D14212694D4DB6651313469F00B47C5A11AB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C7B39D0-F083-4B93-A008-A77924587DC1}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="152">
   <si>
     <t>Method name: LS_241112_Fluorescence_Actino_Sample</t>
   </si>
@@ -475,23 +475,14 @@
     <t>r</t>
   </si>
   <si>
-    <t>DOE 12.7 new 1</t>
-  </si>
-  <si>
-    <t>DOE 12.7 new 2</t>
-  </si>
-  <si>
-    <t>DOE 12.7 new 3</t>
-  </si>
-  <si>
-    <t>DOE 12.7 new 4</t>
+    <t>DOE 12.7</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -504,6 +495,10 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -13997,13 +13992,13 @@
         <v>151</v>
       </c>
       <c r="F351" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G351" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="H351" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I351" t="s">
         <v>151</v>
@@ -14012,22 +14007,22 @@
         <v>151</v>
       </c>
       <c r="K351" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L351" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M351" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="N351" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O351" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="P351" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="Q351" t="s">
         <v>151</v>
@@ -14036,22 +14031,22 @@
         <v>151</v>
       </c>
       <c r="S351" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="T351" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="U351" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="V351" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="W351" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="X351" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="352" spans="1:24" x14ac:dyDescent="0.45">
@@ -14203,6 +14198,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>